--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_23-01-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_23-01-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="127">
   <si>
     <t>SKU</t>
   </si>
@@ -235,6 +235,45 @@
     <t>£53.11</t>
   </si>
   <si>
+    <t>£115.93</t>
+  </si>
+  <si>
+    <t>£23.50</t>
+  </si>
+  <si>
+    <t>£96.35</t>
+  </si>
+  <si>
+    <t>£159.40</t>
+  </si>
+  <si>
+    <t>£35.08</t>
+  </si>
+  <si>
+    <t>£33.23</t>
+  </si>
+  <si>
+    <t>£60.09</t>
+  </si>
+  <si>
+    <t>£27.29</t>
+  </si>
+  <si>
+    <t>£20.54</t>
+  </si>
+  <si>
+    <t>£16.46</t>
+  </si>
+  <si>
+    <t>£29.33</t>
+  </si>
+  <si>
+    <t>£43.58</t>
+  </si>
+  <si>
+    <t>£24.65</t>
+  </si>
+  <si>
     <t>£14.54</t>
   </si>
   <si>
@@ -352,16 +391,7 @@
     <t>£31.3</t>
   </si>
   <si>
-    <t>£54.72</t>
-  </si>
-  <si>
-    <t>£39.99</t>
-  </si>
-  <si>
-    <t>£63.12</t>
-  </si>
-  <si>
-    <t>£66.31</t>
+    <t>Error: HTTPConnectionPool(host='localhost', port=64003): Read timed out. (read timeout=120)</t>
   </si>
   <si>
     <t>£53.91</t>
@@ -801,22 +831,22 @@
         <v>71</v>
       </c>
       <c r="J2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K2" t="s">
         <v>57</v>
       </c>
       <c r="L2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="M2" t="s">
         <v>57</v>
       </c>
       <c r="N2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -848,22 +878,22 @@
         <v>71</v>
       </c>
       <c r="J3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L3" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="M3" t="s">
         <v>57</v>
       </c>
       <c r="N3" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -895,22 +925,22 @@
         <v>71</v>
       </c>
       <c r="J4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="L4" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s">
         <v>57</v>
       </c>
       <c r="N4" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O4" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -942,22 +972,22 @@
         <v>71</v>
       </c>
       <c r="J5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K5" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s">
         <v>57</v>
       </c>
       <c r="N5" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O5" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -989,22 +1019,22 @@
         <v>71</v>
       </c>
       <c r="J6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K6" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="L6" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s">
         <v>57</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O6" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1036,22 +1066,22 @@
         <v>71</v>
       </c>
       <c r="J7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="M7" t="s">
         <v>57</v>
       </c>
       <c r="N7" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O7" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1083,22 +1113,22 @@
         <v>71</v>
       </c>
       <c r="J8" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K8" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="M8" t="s">
         <v>57</v>
       </c>
       <c r="N8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O8" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1130,22 +1160,22 @@
         <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K9" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="M9" t="s">
         <v>57</v>
       </c>
       <c r="N9" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O9" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1177,22 +1207,22 @@
         <v>71</v>
       </c>
       <c r="J10" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K10" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="L10" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s">
         <v>57</v>
       </c>
       <c r="N10" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O10" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1224,22 +1254,22 @@
         <v>71</v>
       </c>
       <c r="J11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="K11" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="L11" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="M11" t="s">
         <v>57</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O11" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1271,22 +1301,22 @@
         <v>71</v>
       </c>
       <c r="J12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="L12" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="M12" t="s">
         <v>57</v>
       </c>
       <c r="N12" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O12" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1318,22 +1348,22 @@
         <v>71</v>
       </c>
       <c r="J13" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K13" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="L13" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s">
         <v>57</v>
       </c>
       <c r="N13" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O13" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1377,7 +1407,7 @@
         <v>57</v>
       </c>
       <c r="N14" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O14" t="s">
         <v>57</v>
@@ -1412,22 +1442,22 @@
         <v>71</v>
       </c>
       <c r="J15" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="K15" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="L15" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="M15" t="s">
         <v>57</v>
       </c>
       <c r="N15" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O15" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -1459,22 +1489,22 @@
         <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L16" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="M16" t="s">
         <v>57</v>
       </c>
       <c r="N16" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -1506,22 +1536,22 @@
         <v>71</v>
       </c>
       <c r="J17" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="L17" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="M17" t="s">
         <v>57</v>
       </c>
       <c r="N17" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O17" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_23-01-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_23-01-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="132">
   <si>
     <t>SKU</t>
   </si>
@@ -235,43 +235,49 @@
     <t>£53.11</t>
   </si>
   <si>
-    <t>£115.93</t>
-  </si>
-  <si>
-    <t>£23.50</t>
-  </si>
-  <si>
-    <t>£96.35</t>
-  </si>
-  <si>
-    <t>£159.40</t>
-  </si>
-  <si>
-    <t>£35.08</t>
-  </si>
-  <si>
-    <t>£33.23</t>
-  </si>
-  <si>
-    <t>£60.09</t>
-  </si>
-  <si>
-    <t>£27.29</t>
-  </si>
-  <si>
-    <t>£20.54</t>
-  </si>
-  <si>
-    <t>£16.46</t>
-  </si>
-  <si>
-    <t>£29.33</t>
-  </si>
-  <si>
-    <t>£43.58</t>
-  </si>
-  <si>
-    <t>£24.65</t>
+    <t>£ 22.50</t>
+  </si>
+  <si>
+    <t>£ 27.07</t>
+  </si>
+  <si>
+    <t>£ 31.26</t>
+  </si>
+  <si>
+    <t>£ 32.98</t>
+  </si>
+  <si>
+    <t>£ 41.07</t>
+  </si>
+  <si>
+    <t>£ 47.43</t>
+  </si>
+  <si>
+    <t>£ 49.60</t>
+  </si>
+  <si>
+    <t>£ 54.47</t>
+  </si>
+  <si>
+    <t>£ 58.97</t>
+  </si>
+  <si>
+    <t>£ 52.54</t>
+  </si>
+  <si>
+    <t>£ 76.45</t>
+  </si>
+  <si>
+    <t>£ 75.36</t>
+  </si>
+  <si>
+    <t>£ 85.62</t>
+  </si>
+  <si>
+    <t>£ 90.96</t>
+  </si>
+  <si>
+    <t>£ 92.81</t>
   </si>
   <si>
     <t>£14.54</t>
@@ -391,7 +397,16 @@
     <t>£31.3</t>
   </si>
   <si>
-    <t>Error: HTTPConnectionPool(host='localhost', port=64003): Read timed out. (read timeout=120)</t>
+    <t>£54.72</t>
+  </si>
+  <si>
+    <t>£39.99</t>
+  </si>
+  <si>
+    <t>£63.12</t>
+  </si>
+  <si>
+    <t>£66.31</t>
   </si>
   <si>
     <t>£53.91</t>
@@ -837,16 +852,16 @@
         <v>57</v>
       </c>
       <c r="L2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M2" t="s">
         <v>57</v>
       </c>
       <c r="N2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -881,19 +896,19 @@
         <v>74</v>
       </c>
       <c r="K3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M3" t="s">
         <v>57</v>
       </c>
       <c r="N3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -928,19 +943,19 @@
         <v>75</v>
       </c>
       <c r="K4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M4" t="s">
         <v>57</v>
       </c>
       <c r="N4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -975,19 +990,19 @@
         <v>76</v>
       </c>
       <c r="K5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s">
         <v>57</v>
       </c>
       <c r="N5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1022,19 +1037,19 @@
         <v>77</v>
       </c>
       <c r="K6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s">
         <v>57</v>
       </c>
       <c r="N6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1069,19 +1084,19 @@
         <v>78</v>
       </c>
       <c r="K7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M7" t="s">
         <v>57</v>
       </c>
       <c r="N7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1116,19 +1131,19 @@
         <v>79</v>
       </c>
       <c r="K8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M8" t="s">
         <v>57</v>
       </c>
       <c r="N8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1163,19 +1178,19 @@
         <v>80</v>
       </c>
       <c r="K9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M9" t="s">
         <v>57</v>
       </c>
       <c r="N9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1210,19 +1225,19 @@
         <v>81</v>
       </c>
       <c r="K10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M10" t="s">
         <v>57</v>
       </c>
       <c r="N10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1257,19 +1272,19 @@
         <v>82</v>
       </c>
       <c r="K11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s">
         <v>57</v>
       </c>
       <c r="N11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1301,22 +1316,22 @@
         <v>71</v>
       </c>
       <c r="J12" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M12" t="s">
         <v>57</v>
       </c>
       <c r="N12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1348,22 +1363,22 @@
         <v>71</v>
       </c>
       <c r="J13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M13" t="s">
         <v>57</v>
       </c>
       <c r="N13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1407,7 +1422,7 @@
         <v>57</v>
       </c>
       <c r="N14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O14" t="s">
         <v>57</v>
@@ -1442,22 +1457,22 @@
         <v>71</v>
       </c>
       <c r="J15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M15" t="s">
         <v>57</v>
       </c>
       <c r="N15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O15" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -1489,22 +1504,22 @@
         <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M16" t="s">
         <v>57</v>
       </c>
       <c r="N16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O16" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -1536,22 +1551,22 @@
         <v>71</v>
       </c>
       <c r="J17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M17" t="s">
         <v>57</v>
       </c>
       <c r="N17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O17" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_23-01-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_23-01-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="131">
   <si>
     <t>SKU</t>
   </si>
@@ -229,145 +229,142 @@
     <t>£42.50</t>
   </si>
   <si>
+    <t>POA</t>
+  </si>
+  <si>
+    <t>£53.11</t>
+  </si>
+  <si>
+    <t>£18.75</t>
+  </si>
+  <si>
+    <t>£22.56</t>
+  </si>
+  <si>
+    <t>£26.05</t>
+  </si>
+  <si>
+    <t>£27.48</t>
+  </si>
+  <si>
+    <t>£34.23</t>
+  </si>
+  <si>
+    <t>£39.52</t>
+  </si>
+  <si>
+    <t>£41.33</t>
+  </si>
+  <si>
+    <t>£45.39</t>
+  </si>
+  <si>
+    <t>£49.14</t>
+  </si>
+  <si>
+    <t>£43.78</t>
+  </si>
+  <si>
+    <t>£63.71</t>
+  </si>
+  <si>
+    <t>£62.8</t>
+  </si>
+  <si>
+    <t>£71.35</t>
+  </si>
+  <si>
+    <t>£75.8</t>
+  </si>
+  <si>
+    <t>£77.34</t>
+  </si>
+  <si>
+    <t>Error: list index out of range</t>
+  </si>
+  <si>
+    <t>£10.58</t>
+  </si>
+  <si>
+    <t>£12.82</t>
+  </si>
+  <si>
+    <t>£15.00</t>
+  </si>
+  <si>
+    <t>£16.21</t>
+  </si>
+  <si>
+    <t>£19.76</t>
+  </si>
+  <si>
+    <t>£21.78</t>
+  </si>
+  <si>
+    <t>£22.12</t>
+  </si>
+  <si>
+    <t>£25.01</t>
+  </si>
+  <si>
+    <t>£27.87</t>
+  </si>
+  <si>
+    <t>£27.66</t>
+  </si>
+  <si>
+    <t>£33.22</t>
+  </si>
+  <si>
+    <t>£33.72</t>
+  </si>
+  <si>
+    <t>£40.60</t>
+  </si>
+  <si>
+    <t>£42.15</t>
+  </si>
+  <si>
+    <t>£40.63</t>
+  </si>
+  <si>
+    <t>£19.80</t>
+  </si>
+  <si>
+    <t>£20.28</t>
+  </si>
+  <si>
+    <t>£24.81</t>
+  </si>
+  <si>
+    <t>£26.24</t>
+  </si>
+  <si>
     <t>POA or OOS</t>
   </si>
   <si>
-    <t>£53.11</t>
-  </si>
-  <si>
-    <t>£ 22.50</t>
-  </si>
-  <si>
-    <t>£ 27.07</t>
-  </si>
-  <si>
-    <t>£ 31.26</t>
-  </si>
-  <si>
-    <t>£ 32.98</t>
-  </si>
-  <si>
-    <t>£ 41.07</t>
-  </si>
-  <si>
-    <t>£ 47.43</t>
-  </si>
-  <si>
-    <t>£ 49.60</t>
-  </si>
-  <si>
-    <t>£ 54.47</t>
-  </si>
-  <si>
-    <t>£ 58.97</t>
-  </si>
-  <si>
-    <t>£ 52.54</t>
-  </si>
-  <si>
-    <t>£ 76.45</t>
-  </si>
-  <si>
-    <t>£ 75.36</t>
-  </si>
-  <si>
-    <t>£ 85.62</t>
-  </si>
-  <si>
-    <t>£ 90.96</t>
-  </si>
-  <si>
-    <t>£ 92.81</t>
+    <t>£30.85</t>
+  </si>
+  <si>
+    <t>£38.41</t>
+  </si>
+  <si>
+    <t>£41.24</t>
+  </si>
+  <si>
+    <t>£43.58</t>
+  </si>
+  <si>
+    <t>£46.24</t>
+  </si>
+  <si>
+    <t>£51.77</t>
+  </si>
+  <si>
+    <t>£59.44</t>
   </si>
   <si>
     <t>£14.54</t>
-  </si>
-  <si>
-    <t>£17.48</t>
-  </si>
-  <si>
-    <t>£18.94</t>
-  </si>
-  <si>
-    <t>£23.24</t>
-  </si>
-  <si>
-    <t>£26.16</t>
-  </si>
-  <si>
-    <t>£27.24</t>
-  </si>
-  <si>
-    <t>£29.17</t>
-  </si>
-  <si>
-    <t>£32.49</t>
-  </si>
-  <si>
-    <t>£34.56</t>
-  </si>
-  <si>
-    <t>£38.66</t>
-  </si>
-  <si>
-    <t>£41.91</t>
-  </si>
-  <si>
-    <t>£48.35</t>
-  </si>
-  <si>
-    <t>£50.21</t>
-  </si>
-  <si>
-    <t>£50.55</t>
-  </si>
-  <si>
-    <t>£10.58</t>
-  </si>
-  <si>
-    <t>£12.82</t>
-  </si>
-  <si>
-    <t>£15.00</t>
-  </si>
-  <si>
-    <t>£16.21</t>
-  </si>
-  <si>
-    <t>£19.76</t>
-  </si>
-  <si>
-    <t>£21.78</t>
-  </si>
-  <si>
-    <t>£22.12</t>
-  </si>
-  <si>
-    <t>£25.01</t>
-  </si>
-  <si>
-    <t>£27.87</t>
-  </si>
-  <si>
-    <t>£27.66</t>
-  </si>
-  <si>
-    <t>£33.22</t>
-  </si>
-  <si>
-    <t>£33.72</t>
-  </si>
-  <si>
-    <t>£40.60</t>
-  </si>
-  <si>
-    <t>£42.15</t>
-  </si>
-  <si>
-    <t>£40.63</t>
-  </si>
-  <si>
-    <t>Price Not Found</t>
   </si>
   <si>
     <t>£19.36</t>
@@ -852,16 +849,16 @@
         <v>57</v>
       </c>
       <c r="L2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="M2" t="s">
         <v>57</v>
       </c>
       <c r="N2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="O2" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -899,16 +896,16 @@
         <v>88</v>
       </c>
       <c r="L3" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s">
         <v>57</v>
       </c>
       <c r="N3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O3" t="s">
         <v>117</v>
-      </c>
-      <c r="O3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -943,19 +940,19 @@
         <v>75</v>
       </c>
       <c r="K4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L4" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="M4" t="s">
         <v>57</v>
       </c>
       <c r="N4" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="O4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -990,19 +987,19 @@
         <v>76</v>
       </c>
       <c r="K5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="M5" t="s">
         <v>57</v>
       </c>
       <c r="N5" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="O5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1037,19 +1034,19 @@
         <v>77</v>
       </c>
       <c r="K6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L6" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="M6" t="s">
         <v>57</v>
       </c>
       <c r="N6" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="O6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1084,19 +1081,19 @@
         <v>78</v>
       </c>
       <c r="K7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L7" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="M7" t="s">
         <v>57</v>
       </c>
       <c r="N7" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="O7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1131,19 +1128,19 @@
         <v>79</v>
       </c>
       <c r="K8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L8" t="s">
+        <v>95</v>
+      </c>
+      <c r="M8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" t="s">
         <v>108</v>
       </c>
-      <c r="M8" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" t="s">
-        <v>117</v>
-      </c>
       <c r="O8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1178,19 +1175,19 @@
         <v>80</v>
       </c>
       <c r="K9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L9" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="M9" t="s">
         <v>57</v>
       </c>
       <c r="N9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="O9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1225,19 +1222,19 @@
         <v>81</v>
       </c>
       <c r="K10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="L10" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" t="s">
         <v>110</v>
       </c>
-      <c r="M10" t="s">
-        <v>57</v>
-      </c>
-      <c r="N10" t="s">
-        <v>117</v>
-      </c>
       <c r="O10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1272,19 +1269,19 @@
         <v>82</v>
       </c>
       <c r="K11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s">
+        <v>98</v>
+      </c>
+      <c r="M11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N11" t="s">
         <v>111</v>
       </c>
-      <c r="M11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N11" t="s">
-        <v>117</v>
-      </c>
       <c r="O11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1319,19 +1316,19 @@
         <v>83</v>
       </c>
       <c r="K12" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="L12" t="s">
+        <v>99</v>
+      </c>
+      <c r="M12" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" t="s">
         <v>112</v>
       </c>
-      <c r="M12" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" t="s">
-        <v>117</v>
-      </c>
       <c r="O12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1366,19 +1363,19 @@
         <v>84</v>
       </c>
       <c r="K13" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M13" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" t="s">
         <v>113</v>
       </c>
-      <c r="M13" t="s">
-        <v>57</v>
-      </c>
-      <c r="N13" t="s">
-        <v>117</v>
-      </c>
       <c r="O13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1422,7 +1419,7 @@
         <v>57</v>
       </c>
       <c r="N14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="O14" t="s">
         <v>57</v>
@@ -1460,19 +1457,19 @@
         <v>85</v>
       </c>
       <c r="K15" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="L15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" t="s">
         <v>114</v>
       </c>
-      <c r="M15" t="s">
-        <v>57</v>
-      </c>
-      <c r="N15" t="s">
-        <v>117</v>
-      </c>
       <c r="O15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -1507,19 +1504,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="L16" t="s">
+        <v>102</v>
+      </c>
+      <c r="M16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" t="s">
         <v>115</v>
       </c>
-      <c r="M16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N16" t="s">
-        <v>117</v>
-      </c>
       <c r="O16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -1554,19 +1551,19 @@
         <v>87</v>
       </c>
       <c r="K17" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="L17" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="M17" t="s">
         <v>57</v>
       </c>
       <c r="N17" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="O17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
